--- a/extenbooks/ES1703.xlsx
+++ b/extenbooks/ES1703.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 8</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1972–1995</t>
+          <t>1972-1995</t>
         </is>
       </c>
     </row>
@@ -834,174 +834,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1703-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cronin 2001 RPE Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1703 — NZ Value Composition of Capital (Cronin 2001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Cronin 2001 RPE Table 2)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1703 — NZ Value Composition of Capital (Cronin 2001)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1972, 1995]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Chapter**: External study (Cronin 2001 RPE Table 2)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1972, 1995]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: share</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cronin Table 2, NZ value composition (C/V). Percent.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cronin Table 2, NZ value composition (C/V). Percent.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1703_nz_value_composition_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1703_nz_value_composition_cronin2001.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1703_nz_value_composition_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1703_nz_value_composition_cronin2001.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1703 -&gt; data/intermediate/ES1703.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1703 -&gt; data/final/ES1703.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1703 -&gt; data/intermediate/validation/ES1703.json</t>
+          <t>data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv</t>
         </is>
       </c>
     </row>
@@ -1017,53 +1018,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1703 -&gt; data/intermediate/ES1703.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1703 -&gt; data/final/ES1703.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1703 -&gt; data/intermediate/validation/ES1703.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1080,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1108,172 +1133,216 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>c/v is the value composition of capital — the ratio of constant capital to variable capital. Constant capital (c) is material inputs into production: intermediate consumption of productive industries plus depreciation of fixed capital (wear and tear of machinery in production). Variable capital (v) is wage payments to productive workers only. c/v is expressed as a percentage (e.g., 293% means constant capital is 2.93 times variable capital). Derived via Shaikh-Tonak methodology applied to NZSNA data for 25 NZ production groups.</t>
+          <t>The 1972-83 decline is related to: A 20% rise in value composition of capital (c/v); Alongside a fairly constant rate of surplus-value (s/v) (see Table 2 and Fig. 11); That is, classic conditions for a falling rate of profit (Marx, 1859, Pt. 3).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Constant Capital, Variable Capital); SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 5 (1972-83 Decline)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Series ES1703-A: Digitized from Cronin (2001) Table 2, column c/v, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are stored as decimals (e.g., 293% = 2.93).</t>
+          <t>The 1984-89 rise in surplus value is associated with: The 37% rise in the rate of surplus-value over the same period; A 12% fall in the value composition of capital between 1985 and 1989 as recession devalued and wrote-off constant capital.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
+          <t>Cronin_2001, body_text.md Section 5 (1984-89 Rise)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Annual c/v values (decimal): 1972=2.93, 1973=3.08, 1974=3.19, 1975=3.06, 1976=3.26, 1977=3.53, 1978=3.46, 1979=3.34, 1980=3.45, 1981=3.44, 1982=3.44, 1983=3.55, 1984=3.85, 1985=4.07, 1986=3.97, 1987=3.73, 1988=3.62, 1989=3.56, 1990=3.57, 1991=3.56, 1992=3.63, 1993=3.84, 1994=3.98, 1995=3.97.</t>
+          <t>Pearce also overestimates the classical category constant capital by including: The wages and salaries of non-productive workers; The stock of fixed capital (Pearce, 1986, pp. 308, 341). Whereas on an annual basis, only the depreciation of fixed capital should be included. Pearce's estimates of the value composition of capital are thus six to eight times those of Shaikh &amp; Tonak for the United States and those in this study (see Fig. 8). The inclusion of (annually accumulating) fixed capital stocks in the definition of constant capital also leads Pearce wrongly to perceive a rise in the value composition of capital in the 1950s and 60s.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv</t>
+          <t>Cronin_2001, body_text.md Section 4 (Comparison with Earlier Studies)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>periodization</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Three phases: (1) 1972-1983 — c/v rose approximately 20% from 293% to 355%, the primary driver of the profitability crisis as rising capital intensity squeezed the surplus share; rate of surplus-value was roughly stable, so the rising composition drove falling accumulation rate. (2) 1984-1989 — c/v fell 12% from peak 407% (1985) to 356% (1989) as recession devalued and wrote off constant capital (equipment write-offs, asset devaluations); this capital devaluation combined with rising s/v to boost the accumulation rate. (3) 1990-1995 — c/v rose again from 357% to 397%, renewed rise offsetting the continuing increase in s/v and causing accumulation rate to plateau at 38%.</t>
+          <t>The classical category of constant capital consists of the material inputs into production, that is the portion of intermediate consumption used in the productive industries. This can be derived simply from the official accounts item 'intermediate production' by: Deducting the intermediate production not attributable to productive industries and the 'trading sector'; Adding the depreciation of fixed capital, representing the wear and tear or use over time of machinery in the course of production, which is recorded in the official accounts as part of value added (see Shaikh &amp; Tonak, 1994, pp. 47-48).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 3 (Constant Capital)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c/v rose from 293% in 1972 to 397% in 1995, a 36% increase. NZ c/v is notably higher than USA estimates from Shaikh-Tonak (290-410% vs 240-300%), indicating a more capital-intensive productive sector. The 1985 peak of 407% represents the highest value composition recorded, followed by recession-driven write-offs pulling it down to 356% by 1989 before resuming its upward trend through the 1990s.</t>
+          <t>c/v is the value composition of capital — the ratio of constant capital to variable capital. Constant capital (c) is material inputs into production: intermediate consumption of productive industries plus depreciation of fixed capital (wear and tear of machinery in production). Variable capital (v) is wage payments to productive workers only. c/v is expressed as a percentage (e.g., 293% means constant capital is 2.93 times variable capital). Derived via Shaikh-Tonak methodology applied to NZSNA data for 25 NZ production groups.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, SUMMARY.md; body_text.md Section 4</t>
+          <t>Cronin_2001, body_text.md Section 3 (Constant Capital, Variable Capital); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pearce (1986) drastically overestimated c/v, arriving at estimates 6-8 times higher than Cronin (and than Shaikh-Tonak's USA estimates), because Pearce included the annual stock of fixed capital rather than just depreciation in constant capital. Using stocks instead of flows inflates c enormously and creates a spurious perception of rising c/v in the 1950s-1960s.</t>
+          <t>Series ES1703-A: Digitized from Cronin (2001) Table 2, column c/v, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are stored as decimals (e.g., 293% = 2.93).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 4 (Comparison with Earlier Studies)</t>
+          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cronin Fig 11: plots c/v alongside s/v for 1972-1995, showing the divergent dynamics — c/v rising in the crisis period, falling mid-1980s with write-offs, rising again post-1991. The figure illustrates the classical squeeze: rising composition offsetting rising exploitation.</t>
+          <t>Annual c/v values (decimal): 1972=2.93, 1973=3.08, 1974=3.19, 1975=3.06, 1976=3.26, 1977=3.53, 1978=3.46, 1979=3.34, 1980=3.45, 1981=3.44, 1982=3.44, 1983=3.55, 1984=3.85, 1985=4.07, 1986=3.97, 1987=3.73, 1988=3.62, 1989=3.56, 1990=3.57, 1991=3.56, 1992=3.63, 1993=3.84, 1994=3.98, 1995=3.97.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Cronin_2001, Table 2; tables.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>periodization</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Three phases: (1) 1972-1983 — c/v rose approximately 20% from 293% to 355%, the primary driver of the profitability crisis as rising capital intensity squeezed the surplus share; rate of surplus-value was roughly stable, so the rising composition drove falling accumulation rate. (2) 1984-1989 — c/v fell 12% from peak 407% (1985) to 356% (1989) as recession devalued and wrote off constant capital (equipment write-offs, asset devaluations); this capital devaluation combined with rising s/v to boost the accumulation rate. (3) 1990-1995 — c/v rose again from 357% to 397%, renewed rise offsetting the continuing increase in s/v and causing accumulation rate to plateau at 38%.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Value composition of capital (c/v) directly digitized from Cronin (2001) Table 2. Constant capital uses depreciation flows (not capital stocks), following Shaikh-Tonak. Variable capital restricted to productive workers. Applied to 25 NZ production groups from NZSNA, 1972-1995. No extension beyond 1995.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>c/v rose from 293% in 1972 to 397% in 1995, a 36% increase. NZ c/v is notably higher than USA estimates from Shaikh-Tonak (290-410% vs 240-300%), indicating a more capital-intensive productive sector. The 1985 peak of 407% represents the highest value composition recorded, followed by recession-driven write-offs pulling it down to 356% by 1989 before resuming its upward trend through the 1990s.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cronin_2001, SUMMARY.md; body_text.md Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pearce (1986) drastically overestimated c/v, arriving at estimates 6-8 times higher than Cronin (and than Shaikh-Tonak's USA estimates), because Pearce included the annual stock of fixed capital rather than just depreciation in constant capital. Using stocks instead of flows inflates c enormously and creates a spurious perception of rising c/v in the 1950s-1960s.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 4 (Comparison with Earlier Studies)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cronin Fig 11: plots c/v alongside s/v for 1972-1995, showing the divergent dynamics — c/v rising in the crisis period, falling mid-1980s with write-offs, rising again post-1991. The figure illustrates the classical squeeze: rising composition offsetting rising exploitation.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Value composition of capital (c/v) directly digitized from Cronin (2001) Table 2. Constant capital uses depreciation flows (not capital stocks), following Shaikh-Tonak. Variable capital restricted to productive workers. Applied to 25 NZ production groups from NZSNA, 1972-1995. No extension beyond 1995.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>known_issues:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
         <is>
           <t>No post-1995 extension available from this source</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Depreciation-based constant capital is the methodologically correct Shaikh-Tonak approach but differs from capital stock measures used in other traditions; cross-study comparisons require care</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NZSNA category adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1350,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1701</t>
+          <t>Depreciation-based constant capital is the methodologically correct Shaikh-Tonak approach but differs from capital stock measures used in other traditions; cross-study comparisons require care</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1358,69 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>NZSNA category adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES1701</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>ES1702</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>ES1704</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Cronin_2001</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1344,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1407,7 +1500,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1453,6 +1546,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
